--- a/data/trans_orig/P1435-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P1435-Provincia-trans_orig.xlsx
@@ -673,12 +673,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5295</t>
+          <t>5240</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>18879</t>
+          <t>18832</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -688,12 +688,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -708,12 +708,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5295</t>
+          <t>5240</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>18879</t>
+          <t>18832</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -723,12 +723,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,22%</t>
         </is>
       </c>
     </row>
@@ -751,12 +751,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>241959</t>
+          <t>242006</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>255543</t>
+          <t>255598</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,76%</t>
+          <t>92,78%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>97,99%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -786,12 +786,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>241959</t>
+          <t>242006</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>255543</t>
+          <t>255598</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,76%</t>
+          <t>92,78%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>97,99%</t>
         </is>
       </c>
     </row>
@@ -911,12 +911,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>70917</t>
+          <t>69885</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>102887</t>
+          <t>102998</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -926,12 +926,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>13,87%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20,42%</t>
+          <t>20,44%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -946,12 +946,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>70917</t>
+          <t>69885</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>102887</t>
+          <t>102998</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -961,12 +961,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>13,87%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20,42%</t>
+          <t>20,44%</t>
         </is>
       </c>
     </row>
@@ -989,12 +989,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>401062</t>
+          <t>400951</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>433032</t>
+          <t>434064</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1004,12 +1004,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>79,58%</t>
+          <t>79,56%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>85,93%</t>
+          <t>86,13%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1024,12 +1024,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>401062</t>
+          <t>400951</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>433032</t>
+          <t>434064</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1039,12 +1039,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>79,58%</t>
+          <t>79,56%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>85,93%</t>
+          <t>86,13%</t>
         </is>
       </c>
     </row>
@@ -1149,12 +1149,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9669</t>
+          <t>9747</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>24403</t>
+          <t>24825</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1164,12 +1164,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1184,12 +1184,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9669</t>
+          <t>9747</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>24403</t>
+          <t>24825</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,4%</t>
         </is>
       </c>
     </row>
@@ -1227,12 +1227,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>311009</t>
+          <t>310587</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>325743</t>
+          <t>325665</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1242,12 +1242,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,72%</t>
+          <t>92,6%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>97,09%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1262,12 +1262,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>311009</t>
+          <t>310587</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>325743</t>
+          <t>325665</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1277,12 +1277,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,72%</t>
+          <t>92,6%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>97,09%</t>
         </is>
       </c>
     </row>
@@ -1387,12 +1387,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>17792</t>
+          <t>18603</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>37603</t>
+          <t>37347</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1402,12 +1402,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1422,12 +1422,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>17792</t>
+          <t>18603</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>37603</t>
+          <t>37347</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1437,12 +1437,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>10,05%</t>
         </is>
       </c>
     </row>
@@ -1465,12 +1465,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>333853</t>
+          <t>334109</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>353664</t>
+          <t>352853</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1480,12 +1480,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>89,88%</t>
+          <t>89,95%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,21%</t>
+          <t>94,99%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>333853</t>
+          <t>334109</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>353664</t>
+          <t>352853</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1515,12 +1515,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,88%</t>
+          <t>89,95%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,21%</t>
+          <t>94,99%</t>
         </is>
       </c>
     </row>
@@ -1625,12 +1625,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1902</t>
+          <t>1948</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12654</t>
+          <t>13283</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1640,12 +1640,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1902</t>
+          <t>1948</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>12654</t>
+          <t>13283</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,4%</t>
         </is>
       </c>
     </row>
@@ -1703,12 +1703,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>195014</t>
+          <t>194385</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>205766</t>
+          <t>205720</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1718,12 +1718,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,91%</t>
+          <t>93,6%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>99,06%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -1738,12 +1738,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>195014</t>
+          <t>194385</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>205766</t>
+          <t>205720</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -1753,12 +1753,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>93,91%</t>
+          <t>93,6%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>99,06%</t>
         </is>
       </c>
     </row>
@@ -1863,12 +1863,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>15694</t>
+          <t>14806</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>34008</t>
+          <t>33586</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -1878,12 +1878,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>12,08%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -1898,12 +1898,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>15694</t>
+          <t>14806</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>34008</t>
+          <t>33586</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -1913,12 +1913,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>12,08%</t>
         </is>
       </c>
     </row>
@@ -1941,12 +1941,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>244136</t>
+          <t>244558</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>262450</t>
+          <t>263338</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>87,77%</t>
+          <t>87,92%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>94,36%</t>
+          <t>94,68%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -1976,12 +1976,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>244136</t>
+          <t>244558</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>262450</t>
+          <t>263338</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -1991,12 +1991,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>87,77%</t>
+          <t>87,92%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>94,36%</t>
+          <t>94,68%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>20679</t>
+          <t>21031</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>42654</t>
+          <t>43748</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>20679</t>
+          <t>21031</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>42654</t>
+          <t>43748</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,85%</t>
         </is>
       </c>
     </row>
@@ -2179,12 +2179,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>595565</t>
+          <t>594471</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>617540</t>
+          <t>617188</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2194,12 +2194,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>93,32%</t>
+          <t>93,15%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>96,76%</t>
+          <t>96,7%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2214,12 +2214,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>595565</t>
+          <t>594471</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>617540</t>
+          <t>617188</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>93,32%</t>
+          <t>93,15%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>96,76%</t>
+          <t>96,7%</t>
         </is>
       </c>
     </row>
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>47803</t>
+          <t>47063</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>78029</t>
+          <t>78406</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -2354,12 +2354,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -2374,12 +2374,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>47803</t>
+          <t>47063</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>78029</t>
+          <t>78406</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -2389,12 +2389,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>10,01%</t>
         </is>
       </c>
     </row>
@@ -2417,12 +2417,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>705482</t>
+          <t>705105</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>735708</t>
+          <t>736448</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -2432,12 +2432,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>90,04%</t>
+          <t>89,99%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>93,9%</t>
+          <t>93,99%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -2452,12 +2452,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>705482</t>
+          <t>705105</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>735708</t>
+          <t>736448</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -2467,12 +2467,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>90,04%</t>
+          <t>89,99%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>93,9%</t>
+          <t>93,99%</t>
         </is>
       </c>
     </row>
@@ -2577,12 +2577,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>229865</t>
+          <t>231258</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>290809</t>
+          <t>290641</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -2612,12 +2612,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>229865</t>
+          <t>231258</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>290809</t>
+          <t>290641</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>8,6%</t>
         </is>
       </c>
     </row>
@@ -2655,12 +2655,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3088388</t>
+          <t>3088556</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3149332</t>
+          <t>3147939</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -2670,12 +2670,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>91,39%</t>
+          <t>91,4%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>93,2%</t>
+          <t>93,16%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -2690,12 +2690,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3088388</t>
+          <t>3088556</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3149332</t>
+          <t>3147939</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>91,39%</t>
+          <t>91,4%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>93,2%</t>
+          <t>93,16%</t>
         </is>
       </c>
     </row>
@@ -2990,12 +2990,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1929</t>
+          <t>1888</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13334</t>
+          <t>13141</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3005,12 +3005,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3025,12 +3025,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1929</t>
+          <t>1888</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>13334</t>
+          <t>13141</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3040,12 +3040,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,57%</t>
         </is>
       </c>
     </row>
@@ -3068,12 +3068,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>273911</t>
+          <t>274104</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>285316</t>
+          <t>285357</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3083,12 +3083,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,36%</t>
+          <t>95,43%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>99,34%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3103,12 +3103,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>273911</t>
+          <t>274104</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>285316</t>
+          <t>285357</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3118,12 +3118,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,36%</t>
+          <t>95,43%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>99,34%</t>
         </is>
       </c>
     </row>
@@ -3228,12 +3228,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>21937</t>
+          <t>21827</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>43929</t>
+          <t>43614</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3243,12 +3243,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3263,12 +3263,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>21937</t>
+          <t>21827</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>43929</t>
+          <t>43614</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,33%</t>
         </is>
       </c>
     </row>
@@ -3306,12 +3306,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>479836</t>
+          <t>480151</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>501828</t>
+          <t>501938</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3321,12 +3321,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,61%</t>
+          <t>91,67%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>95,83%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3341,12 +3341,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>479836</t>
+          <t>480151</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>501828</t>
+          <t>501938</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3356,12 +3356,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,61%</t>
+          <t>91,67%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>95,83%</t>
         </is>
       </c>
     </row>
@@ -3466,12 +3466,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4918</t>
+          <t>4962</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17501</t>
+          <t>17337</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3501,12 +3501,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4918</t>
+          <t>4962</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>17501</t>
+          <t>17337</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,08%</t>
         </is>
       </c>
     </row>
@@ -3544,12 +3544,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>323519</t>
+          <t>323683</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>336102</t>
+          <t>336058</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3559,12 +3559,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,87%</t>
+          <t>94,92%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,54%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3579,12 +3579,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>323519</t>
+          <t>323683</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>336102</t>
+          <t>336058</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3594,12 +3594,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,87%</t>
+          <t>94,92%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,54%</t>
         </is>
       </c>
     </row>
@@ -3704,12 +3704,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7167</t>
+          <t>7649</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>22833</t>
+          <t>23462</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3719,12 +3719,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7167</t>
+          <t>7649</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>22833</t>
+          <t>23462</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3754,12 +3754,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>6,03%</t>
         </is>
       </c>
     </row>
@@ -3782,12 +3782,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>366118</t>
+          <t>365489</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>381784</t>
+          <t>381302</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3797,12 +3797,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,13%</t>
+          <t>93,97%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>98,03%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3817,12 +3817,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>366118</t>
+          <t>365489</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>381784</t>
+          <t>381302</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3832,12 +3832,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,13%</t>
+          <t>93,97%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>98,03%</t>
         </is>
       </c>
     </row>
@@ -3942,12 +3942,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>10811</t>
+          <t>11061</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>27230</t>
+          <t>26385</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -3957,12 +3957,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>12,02%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -3977,12 +3977,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>10811</t>
+          <t>11061</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>27230</t>
+          <t>26385</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -3992,12 +3992,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>12,02%</t>
         </is>
       </c>
     </row>
@@ -4020,12 +4020,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>192361</t>
+          <t>193206</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>208780</t>
+          <t>208530</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4035,12 +4035,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>87,6%</t>
+          <t>87,98%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,08%</t>
+          <t>94,96%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4055,12 +4055,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>192361</t>
+          <t>193206</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>208780</t>
+          <t>208530</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>87,6%</t>
+          <t>87,98%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,08%</t>
+          <t>94,96%</t>
         </is>
       </c>
     </row>
@@ -4180,12 +4180,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>12041</t>
+          <t>12435</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>29159</t>
+          <t>29873</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -4195,12 +4195,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>12041</t>
+          <t>12435</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>29159</t>
+          <t>29873</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -4230,12 +4230,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,74%</t>
         </is>
       </c>
     </row>
@@ -4258,12 +4258,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>248937</t>
+          <t>248223</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>266055</t>
+          <t>265661</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -4273,12 +4273,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>89,51%</t>
+          <t>89,26%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>95,67%</t>
+          <t>95,53%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -4293,12 +4293,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>248937</t>
+          <t>248223</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>266055</t>
+          <t>265661</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -4308,12 +4308,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>89,51%</t>
+          <t>89,26%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>95,67%</t>
+          <t>95,53%</t>
         </is>
       </c>
     </row>
@@ -4418,12 +4418,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>17241</t>
+          <t>17496</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>37676</t>
+          <t>38349</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -4453,12 +4453,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>17241</t>
+          <t>17496</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>37676</t>
+          <t>38349</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,53%</t>
         </is>
       </c>
     </row>
@@ -4496,12 +4496,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>656177</t>
+          <t>655504</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>676612</t>
+          <t>676357</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -4511,12 +4511,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>94,57%</t>
+          <t>94,47%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,48%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -4531,12 +4531,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>656177</t>
+          <t>655504</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>676612</t>
+          <t>676357</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>94,57%</t>
+          <t>94,47%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,48%</t>
         </is>
       </c>
     </row>
@@ -4656,12 +4656,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>7211</t>
+          <t>7107</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>21848</t>
+          <t>21933</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -4671,12 +4671,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -4691,12 +4691,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>7211</t>
+          <t>7107</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>21848</t>
+          <t>21933</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -4706,12 +4706,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,67%</t>
         </is>
       </c>
     </row>
@@ -4734,12 +4734,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>800730</t>
+          <t>800645</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>815367</t>
+          <t>815471</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -4749,12 +4749,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,34%</t>
+          <t>97,33%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,12%</t>
+          <t>99,14%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -4769,12 +4769,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>800730</t>
+          <t>800645</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>815367</t>
+          <t>815471</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -4784,12 +4784,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>97,34%</t>
+          <t>97,33%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>99,12%</t>
+          <t>99,14%</t>
         </is>
       </c>
     </row>
@@ -4894,12 +4894,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>116982</t>
+          <t>115776</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>162900</t>
+          <t>162178</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -4929,12 +4929,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>116982</t>
+          <t>115776</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>162900</t>
+          <t>162178</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -4944,12 +4944,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,56%</t>
         </is>
       </c>
     </row>
@@ -4972,12 +4972,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3392198</t>
+          <t>3392920</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3438116</t>
+          <t>3439322</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -4987,12 +4987,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>95,42%</t>
+          <t>95,44%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>96,74%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -5007,12 +5007,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3392198</t>
+          <t>3392920</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3438116</t>
+          <t>3439322</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -5022,12 +5022,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>95,42%</t>
+          <t>95,44%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>96,74%</t>
         </is>
       </c>
     </row>
@@ -5307,12 +5307,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2795</t>
+          <t>1998</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14206</t>
+          <t>13088</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5322,12 +5322,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5342,12 +5342,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2795</t>
+          <t>1998</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>14206</t>
+          <t>13088</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5357,12 +5357,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,53%</t>
         </is>
       </c>
     </row>
@@ -5385,12 +5385,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>274497</t>
+          <t>275615</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>285908</t>
+          <t>286705</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5400,12 +5400,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,08%</t>
+          <t>95,47%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>99,31%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5420,12 +5420,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>274497</t>
+          <t>275615</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>285908</t>
+          <t>286705</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5435,12 +5435,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,08%</t>
+          <t>95,47%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>99,31%</t>
         </is>
       </c>
     </row>
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>984</t>
+          <t>982</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9753</t>
+          <t>8872</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5565,7 +5565,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5580,12 +5580,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>984</t>
+          <t>982</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9753</t>
+          <t>8872</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5600,7 +5600,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,7%</t>
         </is>
       </c>
     </row>
@@ -5623,12 +5623,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>513331</t>
+          <t>514212</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>522100</t>
+          <t>522102</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5638,7 +5638,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>98,3%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -5658,12 +5658,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>513331</t>
+          <t>514212</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>522100</t>
+          <t>522102</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5673,7 +5673,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>98,3%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -5783,12 +5783,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3599</t>
+          <t>3655</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13805</t>
+          <t>14346</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5798,12 +5798,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5818,12 +5818,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3599</t>
+          <t>3655</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>13805</t>
+          <t>14346</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5833,12 +5833,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,27%</t>
         </is>
       </c>
     </row>
@@ -5861,12 +5861,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>322504</t>
+          <t>321963</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>332710</t>
+          <t>332654</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5876,12 +5876,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,9%</t>
+          <t>95,73%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>98,91%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5896,12 +5896,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>322504</t>
+          <t>321963</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>332710</t>
+          <t>332654</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5911,12 +5911,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,9%</t>
+          <t>95,73%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>98,91%</t>
         </is>
       </c>
     </row>
@@ -6021,12 +6021,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1827</t>
+          <t>1751</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11335</t>
+          <t>10087</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6036,12 +6036,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6056,12 +6056,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1827</t>
+          <t>1751</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11335</t>
+          <t>10087</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6071,12 +6071,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,6%</t>
         </is>
       </c>
     </row>
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>375948</t>
+          <t>377196</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>385456</t>
+          <t>385532</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6114,12 +6114,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,07%</t>
+          <t>97,4%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>99,55%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6134,12 +6134,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>375948</t>
+          <t>377196</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>385456</t>
+          <t>385532</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,07%</t>
+          <t>97,4%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>99,55%</t>
         </is>
       </c>
     </row>
@@ -6259,12 +6259,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>960</t>
+          <t>961</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8711</t>
+          <t>9506</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6279,7 +6279,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6294,12 +6294,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>960</t>
+          <t>961</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>8711</t>
+          <t>9506</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6314,7 +6314,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,35%</t>
         </is>
       </c>
     </row>
@@ -6337,12 +6337,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>209876</t>
+          <t>209081</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>217627</t>
+          <t>217626</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6352,7 +6352,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,01%</t>
+          <t>95,65%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -6372,12 +6372,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>209876</t>
+          <t>209081</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>217627</t>
+          <t>217626</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6387,7 +6387,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,01%</t>
+          <t>95,65%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -6502,7 +6502,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4991</t>
+          <t>4650</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6517,7 +6517,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6537,7 +6537,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4991</t>
+          <t>4650</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6552,7 +6552,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,7%</t>
         </is>
       </c>
     </row>
@@ -6575,7 +6575,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>268124</t>
+          <t>268465</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -6590,7 +6590,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>98,3%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -6610,7 +6610,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>268124</t>
+          <t>268465</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -6625,7 +6625,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>98,3%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>21505</t>
+          <t>21357</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>45436</t>
+          <t>43448</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6750,12 +6750,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6770,12 +6770,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>21505</t>
+          <t>21357</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>45436</t>
+          <t>43448</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6785,12 +6785,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,29%</t>
         </is>
       </c>
     </row>
@@ -6813,12 +6813,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>645858</t>
+          <t>647846</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>669789</t>
+          <t>669937</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6828,12 +6828,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>93,43%</t>
+          <t>93,71%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>96,91%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6848,12 +6848,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>645858</t>
+          <t>647846</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>669789</t>
+          <t>669937</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6863,12 +6863,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>93,43%</t>
+          <t>93,71%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>96,91%</t>
         </is>
       </c>
     </row>
@@ -6973,12 +6973,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>3916</t>
+          <t>3885</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>15093</t>
+          <t>15209</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6993,7 +6993,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7008,12 +7008,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>3916</t>
+          <t>3885</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>15093</t>
+          <t>15209</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7028,7 +7028,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,84%</t>
         </is>
       </c>
     </row>
@@ -7051,12 +7051,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>811074</t>
+          <t>810958</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>822251</t>
+          <t>822282</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -7066,7 +7066,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>98,16%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -7086,12 +7086,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>811074</t>
+          <t>810958</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>822251</t>
+          <t>822282</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -7101,7 +7101,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>98,16%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -7211,12 +7211,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>52831</t>
+          <t>51767</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>84756</t>
+          <t>83952</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7226,12 +7226,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7246,12 +7246,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>52831</t>
+          <t>51767</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>84756</t>
+          <t>83952</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,37%</t>
         </is>
       </c>
     </row>
@@ -7289,12 +7289,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3459786</t>
+          <t>3460590</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3491711</t>
+          <t>3492775</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7304,12 +7304,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>97,63%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
+          <t>98,54%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7324,12 +7324,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3459786</t>
+          <t>3460590</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3491711</t>
+          <t>3492775</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7339,12 +7339,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>97,63%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
+          <t>98,54%</t>
         </is>
       </c>
     </row>
@@ -7619,32 +7619,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>1134</t>
+          <t>1433</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>169</t>
+          <t>421</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3339</t>
+          <t>4183</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7654,32 +7654,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1134</t>
+          <t>1433</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>169</t>
+          <t>421</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3339</t>
+          <t>4183</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,32%</t>
         </is>
       </c>
     </row>
@@ -7697,32 +7697,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>288501</t>
+          <t>314628</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>286296</t>
+          <t>311878</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>289466</t>
+          <t>315640</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>99,61%</t>
+          <t>99,55%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>98,68%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,94%</t>
+          <t>99,87%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7732,32 +7732,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>288501</t>
+          <t>314628</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>286296</t>
+          <t>311878</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>289466</t>
+          <t>315640</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>99,61%</t>
+          <t>99,55%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>98,68%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,94%</t>
+          <t>99,87%</t>
         </is>
       </c>
     </row>
@@ -7775,17 +7775,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7810,17 +7810,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7857,32 +7857,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>31622</t>
+          <t>32684</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>22289</t>
+          <t>22931</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>46592</t>
+          <t>46032</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7892,32 +7892,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>31622</t>
+          <t>32684</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>22289</t>
+          <t>22931</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>46592</t>
+          <t>46032</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>8,5%</t>
         </is>
       </c>
     </row>
@@ -7935,32 +7935,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>478512</t>
+          <t>509030</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>463542</t>
+          <t>495682</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>487845</t>
+          <t>518783</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>93,8%</t>
+          <t>93,97%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>90,87%</t>
+          <t>91,5%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,63%</t>
+          <t>95,77%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7970,32 +7970,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>478512</t>
+          <t>509030</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>463542</t>
+          <t>495682</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>487845</t>
+          <t>518783</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>93,8%</t>
+          <t>93,97%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,87%</t>
+          <t>91,5%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,63%</t>
+          <t>95,77%</t>
         </is>
       </c>
     </row>
@@ -8013,17 +8013,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>510134</t>
+          <t>541714</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>510134</t>
+          <t>541714</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>510134</t>
+          <t>541714</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8048,17 +8048,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>510134</t>
+          <t>541714</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>510134</t>
+          <t>541714</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>510134</t>
+          <t>541714</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8095,32 +8095,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>10240</t>
+          <t>10902</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5602</t>
+          <t>6161</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>18652</t>
+          <t>19535</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8130,32 +8130,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>10240</t>
+          <t>10902</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5602</t>
+          <t>6161</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>18652</t>
+          <t>19535</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,48%</t>
         </is>
       </c>
     </row>
@@ -8173,32 +8173,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>338888</t>
+          <t>345479</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>330476</t>
+          <t>336846</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>343526</t>
+          <t>350220</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>97,07%</t>
+          <t>96,94%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,66%</t>
+          <t>94,52%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,27%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8208,32 +8208,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>338888</t>
+          <t>345479</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>330476</t>
+          <t>336846</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>343526</t>
+          <t>350220</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>97,07%</t>
+          <t>96,94%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,66%</t>
+          <t>94,52%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,27%</t>
         </is>
       </c>
     </row>
@@ -8251,17 +8251,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8286,17 +8286,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8333,32 +8333,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>83570</t>
+          <t>17784</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12915</t>
+          <t>9957</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>232362</t>
+          <t>28522</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>48,91%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8368,32 +8368,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>83570</t>
+          <t>17784</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>12915</t>
+          <t>9957</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>232362</t>
+          <t>28522</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>48,91%</t>
+          <t>6,77%</t>
         </is>
       </c>
     </row>
@@ -8411,32 +8411,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>391520</t>
+          <t>403545</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>242728</t>
+          <t>392807</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>462175</t>
+          <t>411372</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>82,41%</t>
+          <t>95,78%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>51,09%</t>
+          <t>93,23%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>97,64%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8446,32 +8446,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>391520</t>
+          <t>403545</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>242728</t>
+          <t>392807</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>462175</t>
+          <t>411372</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>82,41%</t>
+          <t>95,78%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>51,09%</t>
+          <t>93,23%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>97,64%</t>
         </is>
       </c>
     </row>
@@ -8489,17 +8489,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>475090</t>
+          <t>421329</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>475090</t>
+          <t>421329</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>475090</t>
+          <t>421329</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -8524,17 +8524,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>475090</t>
+          <t>421329</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>475090</t>
+          <t>421329</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>475090</t>
+          <t>421329</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8571,32 +8571,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>18238</t>
+          <t>20292</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>13270</t>
+          <t>14676</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>25076</t>
+          <t>27519</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8606,32 +8606,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>18238</t>
+          <t>20292</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>13270</t>
+          <t>14676</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>25076</t>
+          <t>27519</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>12,13%</t>
         </is>
       </c>
     </row>
@@ -8649,32 +8649,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>190036</t>
+          <t>206531</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>183198</t>
+          <t>199304</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>195004</t>
+          <t>212147</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>91,24%</t>
+          <t>91,05%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>87,96%</t>
+          <t>87,87%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>93,63%</t>
+          <t>93,53%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8684,32 +8684,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>190036</t>
+          <t>206531</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>183198</t>
+          <t>199304</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>195004</t>
+          <t>212147</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>91,24%</t>
+          <t>91,05%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>87,96%</t>
+          <t>87,87%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,63%</t>
+          <t>93,53%</t>
         </is>
       </c>
     </row>
@@ -8727,17 +8727,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>208274</t>
+          <t>226823</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>208274</t>
+          <t>226823</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>208274</t>
+          <t>226823</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8762,17 +8762,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>208274</t>
+          <t>226823</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>208274</t>
+          <t>226823</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>208274</t>
+          <t>226823</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8809,32 +8809,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>11939</t>
+          <t>11579</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6764</t>
+          <t>6504</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>19092</t>
+          <t>18696</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8844,32 +8844,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>11939</t>
+          <t>11579</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>6764</t>
+          <t>6504</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>19092</t>
+          <t>18696</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,11%</t>
         </is>
       </c>
     </row>
@@ -8887,32 +8887,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>244448</t>
+          <t>251520</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>237295</t>
+          <t>244403</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>249623</t>
+          <t>256595</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>95,6%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>92,55%</t>
+          <t>92,89%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,36%</t>
+          <t>97,53%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8922,32 +8922,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>244448</t>
+          <t>251520</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>237295</t>
+          <t>244403</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>249623</t>
+          <t>256595</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>95,6%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>92,55%</t>
+          <t>92,89%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,36%</t>
+          <t>97,53%</t>
         </is>
       </c>
     </row>
@@ -8965,17 +8965,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>256387</t>
+          <t>263099</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>256387</t>
+          <t>263099</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>256387</t>
+          <t>263099</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -9000,17 +9000,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>256387</t>
+          <t>263099</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>256387</t>
+          <t>263099</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>256387</t>
+          <t>263099</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -9047,32 +9047,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>95286</t>
+          <t>117066</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>44305</t>
+          <t>96181</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>133596</t>
+          <t>138364</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>15,25%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>12,53%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>18,02%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9082,32 +9082,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>95286</t>
+          <t>117066</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>44305</t>
+          <t>96181</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>133596</t>
+          <t>138364</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>15,25%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>12,53%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>18,02%</t>
         </is>
       </c>
     </row>
@@ -9125,32 +9125,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>751580</t>
+          <t>650569</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>713270</t>
+          <t>629271</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>802561</t>
+          <t>671454</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>88,75%</t>
+          <t>84,75%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>84,22%</t>
+          <t>81,98%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>94,77%</t>
+          <t>87,47%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9160,32 +9160,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>751580</t>
+          <t>650569</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>713270</t>
+          <t>629271</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>802561</t>
+          <t>671454</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>88,75%</t>
+          <t>84,75%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>84,22%</t>
+          <t>81,98%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>94,77%</t>
+          <t>87,47%</t>
         </is>
       </c>
     </row>
@@ -9203,17 +9203,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>846866</t>
+          <t>767635</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>846866</t>
+          <t>767635</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>846866</t>
+          <t>767635</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9238,17 +9238,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>846866</t>
+          <t>767635</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>846866</t>
+          <t>767635</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>846866</t>
+          <t>767635</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9285,17 +9285,17 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>14797</t>
+          <t>17193</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>8805</t>
+          <t>10474</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>23214</t>
+          <t>26773</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9305,12 +9305,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9320,17 +9320,17 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>14797</t>
+          <t>17193</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>8805</t>
+          <t>10474</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>23214</t>
+          <t>26773</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9340,12 +9340,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,22%</t>
         </is>
       </c>
     </row>
@@ -9363,17 +9363,17 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>700595</t>
+          <t>813416</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>692178</t>
+          <t>803836</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>706587</t>
+          <t>820135</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9383,12 +9383,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>96,76%</t>
+          <t>96,78%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,74%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9398,17 +9398,17 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>700595</t>
+          <t>813416</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>692178</t>
+          <t>803836</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>706587</t>
+          <t>820135</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9418,12 +9418,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>96,76%</t>
+          <t>96,78%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,74%</t>
         </is>
       </c>
     </row>
@@ -9441,17 +9441,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>715392</t>
+          <t>830609</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>715392</t>
+          <t>830609</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>715392</t>
+          <t>830609</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -9476,17 +9476,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>715392</t>
+          <t>830609</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>715392</t>
+          <t>830609</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>715392</t>
+          <t>830609</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -9523,32 +9523,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>266826</t>
+          <t>228933</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>188999</t>
+          <t>201079</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>510642</t>
+          <t>259341</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -9558,32 +9558,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>266826</t>
+          <t>228933</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>188999</t>
+          <t>201079</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>510642</t>
+          <t>259341</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>6,96%</t>
         </is>
       </c>
     </row>
@@ -9601,32 +9601,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>3384078</t>
+          <t>3494719</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3140262</t>
+          <t>3464311</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3461905</t>
+          <t>3522573</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>92,69%</t>
+          <t>93,85%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>86,01%</t>
+          <t>93,04%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>94,82%</t>
+          <t>94,6%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -9636,32 +9636,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>3384078</t>
+          <t>3494719</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3140262</t>
+          <t>3464311</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3461905</t>
+          <t>3522573</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>92,69%</t>
+          <t>93,85%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>86,01%</t>
+          <t>93,04%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>94,82%</t>
+          <t>94,6%</t>
         </is>
       </c>
     </row>
@@ -9679,17 +9679,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>3650904</t>
+          <t>3723652</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3650904</t>
+          <t>3723652</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3650904</t>
+          <t>3723652</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -9714,17 +9714,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3650904</t>
+          <t>3723652</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3650904</t>
+          <t>3723652</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3650904</t>
+          <t>3723652</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
